--- a/FileMau/BangKe.xlsx
+++ b/FileMau/BangKe.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>ĐƠN VỊ:</t>
   </si>
@@ -38,10 +38,7 @@
     <t>CƠ SỞ/BỘ PHẬN</t>
   </si>
   <si>
-    <t>P.Hành chính</t>
-  </si>
-  <si>
-    <t>BẢNG KÊ CHI PHÍ GRAP</t>
+    <t>BẢNG KÊ CHI PHÍ GRAB</t>
   </si>
   <si>
     <t>Từ ngày</t>
@@ -884,7 +881,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Trang tính1-style" pivot="0" count="2" xr9:uid="{F64727C7-5102-492E-BC08-A2DFC36617A5}">
+    <tableStyle name="Trang tính1-style" pivot="0" count="2" xr9:uid="{59C8826D-0913-4BFF-883F-DB65F1E64D30}">
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
@@ -1131,9 +1128,7 @@
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -1147,7 +1142,7 @@
     <row r="3" ht="15" spans="1:12">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1158,10 +1153,10 @@
     <row r="4" ht="15" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -1176,10 +1171,10 @@
     <row r="5" ht="15" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -1193,7 +1188,7 @@
     </row>
     <row r="6" ht="15" spans="1:12">
       <c r="A6" s="15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1209,43 +1204,43 @@
     </row>
     <row r="7" ht="28.5" spans="1:13">
       <c r="A7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1" spans="1:13">
